--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121974048</v>
+        <v>121974049</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626654</v>
+        <v>626642</v>
       </c>
       <c r="R3" t="n">
-        <v>6706333</v>
+        <v>6706342</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974053</v>
+        <v>121974051</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626654</v>
+        <v>626648</v>
       </c>
       <c r="R4" t="n">
-        <v>6706447</v>
+        <v>6706412</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974054</v>
+        <v>121974055</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626643</v>
+        <v>626657</v>
       </c>
       <c r="R5" t="n">
-        <v>6706452</v>
+        <v>6706616</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974526</v>
+        <v>121974527</v>
       </c>
       <c r="B6" t="n">
         <v>95660</v>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626642</v>
+        <v>626644</v>
       </c>
       <c r="R6" t="n">
-        <v>6706310</v>
+        <v>6706360</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974525</v>
+        <v>121974053</v>
       </c>
       <c r="B7" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1265,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626657</v>
+        <v>626654</v>
       </c>
       <c r="R7" t="n">
-        <v>6706616</v>
+        <v>6706447</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1337,6 +1353,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974049</v>
+        <v>121974525</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,54 +1384,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626642</v>
+        <v>626657</v>
       </c>
       <c r="R8" t="n">
-        <v>6706342</v>
+        <v>6706616</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1455,7 +1456,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974527</v>
+        <v>121974047</v>
       </c>
       <c r="B10" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1605,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626644</v>
+        <v>626642</v>
       </c>
       <c r="R10" t="n">
-        <v>6706360</v>
+        <v>6706310</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1677,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1695,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121974051</v>
+        <v>121974048</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1730,7 +1747,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1751,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626654</v>
       </c>
       <c r="R11" t="n">
-        <v>6706412</v>
+        <v>6706333</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1814,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974047</v>
+        <v>121974054</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1849,12 +1866,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1870,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626642</v>
+        <v>626643</v>
       </c>
       <c r="R12" t="n">
-        <v>6706310</v>
+        <v>6706452</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1933,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974055</v>
+        <v>121974526</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>95660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,54 +1962,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626657</v>
+        <v>626642</v>
       </c>
       <c r="R13" t="n">
-        <v>6706616</v>
+        <v>6706310</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2033,7 +2034,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121974050</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121974049</v>
+        <v>121974051</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626642</v>
+        <v>626648</v>
       </c>
       <c r="R3" t="n">
-        <v>6706342</v>
+        <v>6706412</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974051</v>
+        <v>121974047</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626648</v>
+        <v>626642</v>
       </c>
       <c r="R4" t="n">
-        <v>6706412</v>
+        <v>6706310</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974055</v>
+        <v>121974054</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626657</v>
+        <v>626643</v>
       </c>
       <c r="R5" t="n">
-        <v>6706616</v>
+        <v>6706452</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974527</v>
+        <v>121974526</v>
       </c>
       <c r="B6" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626644</v>
+        <v>626642</v>
       </c>
       <c r="R6" t="n">
-        <v>6706360</v>
+        <v>6706310</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974053</v>
+        <v>121974525</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>105236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,54 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626654</v>
+        <v>626657</v>
       </c>
       <c r="R7" t="n">
-        <v>6706447</v>
+        <v>6706616</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1353,7 +1337,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974525</v>
+        <v>121974053</v>
       </c>
       <c r="B8" t="n">
-        <v>105218</v>
+        <v>98131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1367,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626657</v>
+        <v>626654</v>
       </c>
       <c r="R8" t="n">
-        <v>6706616</v>
+        <v>6706447</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1456,6 +1455,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>121974052</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974047</v>
+        <v>121974527</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>95678</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,54 +1605,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626642</v>
+        <v>626644</v>
       </c>
       <c r="R10" t="n">
-        <v>6706310</v>
+        <v>6706360</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,7 +1677,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1712,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121974048</v>
+        <v>121974049</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,7 +1730,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1768,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626654</v>
+        <v>626642</v>
       </c>
       <c r="R11" t="n">
-        <v>6706333</v>
+        <v>6706342</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1831,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974054</v>
+        <v>121974048</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,12 +1849,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1887,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626643</v>
+        <v>626654</v>
       </c>
       <c r="R12" t="n">
-        <v>6706452</v>
+        <v>6706333</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1950,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974526</v>
+        <v>121974055</v>
       </c>
       <c r="B13" t="n">
-        <v>95660</v>
+        <v>98131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,38 +1945,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626642</v>
+        <v>626657</v>
       </c>
       <c r="R13" t="n">
-        <v>6706310</v>
+        <v>6706616</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,6 +2033,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974052</v>
+        <v>121974527</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>95678</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,54 +1486,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626657</v>
+        <v>626644</v>
       </c>
       <c r="R9" t="n">
-        <v>6706425</v>
+        <v>6706360</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1558,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1593,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974527</v>
+        <v>121974052</v>
       </c>
       <c r="B10" t="n">
-        <v>95678</v>
+        <v>98131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1588,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626644</v>
+        <v>626657</v>
       </c>
       <c r="R10" t="n">
-        <v>6706360</v>
+        <v>6706425</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1677,6 +1676,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121974052</v>
+        <v>121974525</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>105280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,44 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
@@ -734,7 +718,7 @@
         <v>626657</v>
       </c>
       <c r="R2" t="n">
-        <v>6706425</v>
+        <v>6706616</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121974049</v>
+        <v>121974526</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>95722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,44 +789,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
@@ -853,7 +820,7 @@
         <v>626642</v>
       </c>
       <c r="R3" t="n">
-        <v>6706342</v>
+        <v>6706310</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -894,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974053</v>
+        <v>121974048</v>
       </c>
       <c r="B4" t="n">
         <v>98175</v>
@@ -948,7 +914,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,7 +924,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -972,7 +938,7 @@
         <v>626654</v>
       </c>
       <c r="R4" t="n">
-        <v>6706447</v>
+        <v>6706333</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974050</v>
+        <v>121974047</v>
       </c>
       <c r="B5" t="n">
         <v>98175</v>
@@ -1067,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1088,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626644</v>
+        <v>626642</v>
       </c>
       <c r="R5" t="n">
-        <v>6706360</v>
+        <v>6706310</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974048</v>
+        <v>121974527</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>95722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,54 +1129,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626654</v>
+        <v>626644</v>
       </c>
       <c r="R6" t="n">
-        <v>6706333</v>
+        <v>6706360</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1251,7 +1201,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974525</v>
+        <v>121974049</v>
       </c>
       <c r="B7" t="n">
-        <v>105280</v>
+        <v>98175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1231,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626657</v>
+        <v>626642</v>
       </c>
       <c r="R7" t="n">
-        <v>6706616</v>
+        <v>6706342</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1354,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974051</v>
+        <v>121974050</v>
       </c>
       <c r="B8" t="n">
         <v>98175</v>
@@ -1407,7 +1373,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1428,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626648</v>
+        <v>626644</v>
       </c>
       <c r="R8" t="n">
-        <v>6706412</v>
+        <v>6706360</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1491,7 +1457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974055</v>
+        <v>121974051</v>
       </c>
       <c r="B9" t="n">
         <v>98175</v>
@@ -1526,7 +1492,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1547,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626657</v>
+        <v>626648</v>
       </c>
       <c r="R9" t="n">
-        <v>6706616</v>
+        <v>6706412</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1610,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974054</v>
+        <v>121974055</v>
       </c>
       <c r="B10" t="n">
         <v>98175</v>
@@ -1645,12 +1611,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1666,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626643</v>
+        <v>626657</v>
       </c>
       <c r="R10" t="n">
-        <v>6706452</v>
+        <v>6706616</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1729,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121974527</v>
+        <v>121974053</v>
       </c>
       <c r="B11" t="n">
-        <v>95722</v>
+        <v>98175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,38 +1707,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626644</v>
+        <v>626654</v>
       </c>
       <c r="R11" t="n">
-        <v>6706360</v>
+        <v>6706447</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1813,6 +1795,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1831,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974047</v>
+        <v>121974054</v>
       </c>
       <c r="B12" t="n">
         <v>98175</v>
@@ -1866,12 +1849,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1887,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626642</v>
+        <v>626643</v>
       </c>
       <c r="R12" t="n">
-        <v>6706310</v>
+        <v>6706452</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1950,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974526</v>
+        <v>121974052</v>
       </c>
       <c r="B13" t="n">
-        <v>95722</v>
+        <v>98175</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,38 +1945,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626642</v>
+        <v>626657</v>
       </c>
       <c r="R13" t="n">
-        <v>6706310</v>
+        <v>6706425</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,6 +2033,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121974525</v>
+        <v>121974527</v>
       </c>
       <c r="B2" t="n">
-        <v>105280</v>
+        <v>95732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626657</v>
+        <v>626644</v>
       </c>
       <c r="R2" t="n">
-        <v>6706616</v>
+        <v>6706360</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121974526</v>
+        <v>121974048</v>
       </c>
       <c r="B3" t="n">
-        <v>95722</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626642</v>
+        <v>626654</v>
       </c>
       <c r="R3" t="n">
-        <v>6706310</v>
+        <v>6706333</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974048</v>
+        <v>121974055</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -935,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626654</v>
+        <v>626657</v>
       </c>
       <c r="R4" t="n">
-        <v>6706333</v>
+        <v>6706616</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974047</v>
+        <v>121974053</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1043,7 +1060,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1054,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626642</v>
+        <v>626654</v>
       </c>
       <c r="R5" t="n">
-        <v>6706310</v>
+        <v>6706447</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1117,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974527</v>
+        <v>121974051</v>
       </c>
       <c r="B6" t="n">
-        <v>95722</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,38 +1146,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626644</v>
+        <v>626648</v>
       </c>
       <c r="R6" t="n">
-        <v>6706360</v>
+        <v>6706412</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,6 +1234,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974049</v>
+        <v>121974525</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>105290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,54 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626642</v>
+        <v>626657</v>
       </c>
       <c r="R7" t="n">
-        <v>6706342</v>
+        <v>6706616</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1319,7 +1337,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974050</v>
+        <v>121974526</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>95732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,54 +1367,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626644</v>
+        <v>626642</v>
       </c>
       <c r="R8" t="n">
-        <v>6706360</v>
+        <v>6706310</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,7 +1439,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974051</v>
+        <v>121974054</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626648</v>
+        <v>626643</v>
       </c>
       <c r="R9" t="n">
-        <v>6706412</v>
+        <v>6706452</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974055</v>
+        <v>121974050</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626657</v>
+        <v>626644</v>
       </c>
       <c r="R10" t="n">
-        <v>6706616</v>
+        <v>6706360</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121974053</v>
+        <v>121974052</v>
       </c>
       <c r="B11" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626654</v>
+        <v>626657</v>
       </c>
       <c r="R11" t="n">
-        <v>6706447</v>
+        <v>6706425</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974054</v>
+        <v>121974047</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626643</v>
+        <v>626642</v>
       </c>
       <c r="R12" t="n">
-        <v>6706452</v>
+        <v>6706310</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974052</v>
+        <v>121974049</v>
       </c>
       <c r="B13" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626657</v>
+        <v>626642</v>
       </c>
       <c r="R13" t="n">
-        <v>6706425</v>
+        <v>6706342</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121974527</v>
+        <v>121974526</v>
       </c>
       <c r="B2" t="n">
         <v>95732</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626644</v>
+        <v>626642</v>
       </c>
       <c r="R2" t="n">
-        <v>6706360</v>
+        <v>6706310</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121974048</v>
+        <v>121974053</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -836,7 +836,7 @@
         <v>626654</v>
       </c>
       <c r="R3" t="n">
-        <v>6706333</v>
+        <v>6706447</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974055</v>
+        <v>121974525</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>105290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,44 +908,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
@@ -996,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974053</v>
+        <v>121974052</v>
       </c>
       <c r="B5" t="n">
         <v>98185</v>
@@ -1050,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1060,7 +1043,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1071,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626654</v>
+        <v>626657</v>
       </c>
       <c r="R5" t="n">
-        <v>6706447</v>
+        <v>6706425</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1134,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974051</v>
+        <v>121974054</v>
       </c>
       <c r="B6" t="n">
         <v>98185</v>
@@ -1169,12 +1152,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1190,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626648</v>
+        <v>626643</v>
       </c>
       <c r="R6" t="n">
-        <v>6706412</v>
+        <v>6706452</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1253,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974525</v>
+        <v>121974049</v>
       </c>
       <c r="B7" t="n">
-        <v>105290</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1248,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626657</v>
+        <v>626642</v>
       </c>
       <c r="R7" t="n">
-        <v>6706616</v>
+        <v>6706342</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1337,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974526</v>
+        <v>121974050</v>
       </c>
       <c r="B8" t="n">
-        <v>95732</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,38 +1367,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626642</v>
+        <v>626644</v>
       </c>
       <c r="R8" t="n">
-        <v>6706310</v>
+        <v>6706360</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1439,6 +1455,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1457,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974054</v>
+        <v>121974527</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>95732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,54 +1486,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626643</v>
+        <v>626644</v>
       </c>
       <c r="R9" t="n">
-        <v>6706452</v>
+        <v>6706360</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1557,7 +1558,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974050</v>
+        <v>121974055</v>
       </c>
       <c r="B10" t="n">
         <v>98185</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626644</v>
+        <v>626657</v>
       </c>
       <c r="R10" t="n">
-        <v>6706360</v>
+        <v>6706616</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121974052</v>
+        <v>121974047</v>
       </c>
       <c r="B11" t="n">
         <v>98185</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626657</v>
+        <v>626642</v>
       </c>
       <c r="R11" t="n">
-        <v>6706425</v>
+        <v>6706310</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974047</v>
+        <v>121974048</v>
       </c>
       <c r="B12" t="n">
         <v>98185</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626642</v>
+        <v>626654</v>
       </c>
       <c r="R12" t="n">
-        <v>6706310</v>
+        <v>6706333</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974049</v>
+        <v>121974051</v>
       </c>
       <c r="B13" t="n">
         <v>98185</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626642</v>
+        <v>626648</v>
       </c>
       <c r="R13" t="n">
-        <v>6706342</v>
+        <v>6706412</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121974526</v>
       </c>
       <c r="B2" t="n">
-        <v>95732</v>
+        <v>95744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121974053</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121974525</v>
+        <v>121974048</v>
       </c>
       <c r="B4" t="n">
-        <v>105290</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,38 +908,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626657</v>
+        <v>626654</v>
       </c>
       <c r="R4" t="n">
-        <v>6706616</v>
+        <v>6706333</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,7 +1018,7 @@
         <v>121974052</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974054</v>
+        <v>121974049</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,12 +1169,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1173,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626643</v>
+        <v>626642</v>
       </c>
       <c r="R6" t="n">
-        <v>6706452</v>
+        <v>6706342</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1236,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974049</v>
+        <v>121974055</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,7 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1292,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626642</v>
+        <v>626657</v>
       </c>
       <c r="R7" t="n">
-        <v>6706342</v>
+        <v>6706616</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974050</v>
+        <v>121974054</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,12 +1407,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1411,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626644</v>
+        <v>626643</v>
       </c>
       <c r="R8" t="n">
-        <v>6706360</v>
+        <v>6706452</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1474,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974527</v>
+        <v>121974525</v>
       </c>
       <c r="B9" t="n">
-        <v>95732</v>
+        <v>105303</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1503,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626644</v>
+        <v>626657</v>
       </c>
       <c r="R9" t="n">
-        <v>6706360</v>
+        <v>6706616</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1576,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121974055</v>
+        <v>121974527</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>95744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,54 +1605,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Båtfors norr om reservatet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626657</v>
+        <v>626644</v>
       </c>
       <c r="R10" t="n">
-        <v>6706616</v>
+        <v>6706360</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,7 +1677,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>121974047</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121974048</v>
+        <v>121974051</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626654</v>
+        <v>626648</v>
       </c>
       <c r="R12" t="n">
-        <v>6706333</v>
+        <v>6706412</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121974051</v>
+        <v>121974050</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626648</v>
+        <v>626644</v>
       </c>
       <c r="R13" t="n">
-        <v>6706412</v>
+        <v>6706360</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2050,6 +2050,1252 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122887165</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626634</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122882318</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95901</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626645</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6706570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122882212</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626670</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706513</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122882189</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626668</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706516</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122882270</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626653</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706538</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122882167</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626699</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706548</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122887244</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626638</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706452</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122882235</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74855</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626655</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706513</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122887317</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57428</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626668</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6706440</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122887301</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95901</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626668</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6706440</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122887268</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626653</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6706454</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,7 +2052,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122887165</v>
+        <v>122882189</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626634</v>
+        <v>626668</v>
       </c>
       <c r="R14" t="n">
-        <v>6706458</v>
+        <v>6706516</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882318</v>
+        <v>122887317</v>
       </c>
       <c r="B15" t="n">
-        <v>95901</v>
+        <v>57428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,38 +2176,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>102621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R15" t="n">
-        <v>6706570</v>
+        <v>6706440</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,7 +2402,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122882189</v>
+        <v>122887244</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2428,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626668</v>
+        <v>626638</v>
       </c>
       <c r="R17" t="n">
-        <v>6706516</v>
+        <v>6706452</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2514,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882270</v>
+        <v>122887268</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2543,7 +2557,7 @@
         <v>626653</v>
       </c>
       <c r="R18" t="n">
-        <v>6706538</v>
+        <v>6706454</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882167</v>
+        <v>122882318</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>95901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,25 +2638,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626699</v>
+        <v>626645</v>
       </c>
       <c r="R19" t="n">
-        <v>6706548</v>
+        <v>6706570</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2724,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122887244</v>
+        <v>122882235</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>74855</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626638</v>
+        <v>626655</v>
       </c>
       <c r="R20" t="n">
-        <v>6706452</v>
+        <v>6706513</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882235</v>
+        <v>122882167</v>
       </c>
       <c r="B21" t="n">
-        <v>74855</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2862,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626655</v>
+        <v>626699</v>
       </c>
       <c r="R21" t="n">
-        <v>6706513</v>
+        <v>6706548</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2948,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887317</v>
+        <v>122887301</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>95901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,42 +2974,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887301</v>
+        <v>122882270</v>
       </c>
       <c r="B23" t="n">
-        <v>95901</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R23" t="n">
-        <v>6706440</v>
+        <v>6706538</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,7 +3186,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887268</v>
+        <v>122887165</v>
       </c>
       <c r="B24" t="n">
         <v>98355</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626653</v>
+        <v>626634</v>
       </c>
       <c r="R24" t="n">
-        <v>6706454</v>
+        <v>6706458</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882189</v>
+        <v>122887317</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>57428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,28 +2064,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -2095,7 +2109,7 @@
         <v>626668</v>
       </c>
       <c r="R14" t="n">
-        <v>6706516</v>
+        <v>6706440</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122887317</v>
+        <v>122882235</v>
       </c>
       <c r="B15" t="n">
-        <v>57428</v>
+        <v>74855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,52 +2190,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102621</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626668</v>
+        <v>626655</v>
       </c>
       <c r="R15" t="n">
-        <v>6706440</v>
+        <v>6706513</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882212</v>
+        <v>122887244</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626670</v>
+        <v>626638</v>
       </c>
       <c r="R16" t="n">
-        <v>6706513</v>
+        <v>6706452</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887244</v>
+        <v>122887165</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626638</v>
+        <v>626634</v>
       </c>
       <c r="R17" t="n">
-        <v>6706452</v>
+        <v>6706458</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122887268</v>
+        <v>122882167</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626653</v>
+        <v>626699</v>
       </c>
       <c r="R18" t="n">
-        <v>6706454</v>
+        <v>6706548</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882318</v>
+        <v>122887301</v>
       </c>
       <c r="B19" t="n">
-        <v>95901</v>
+        <v>95903</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R19" t="n">
-        <v>6706570</v>
+        <v>6706440</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882235</v>
+        <v>122882270</v>
       </c>
       <c r="B20" t="n">
-        <v>74855</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626655</v>
+        <v>626653</v>
       </c>
       <c r="R20" t="n">
-        <v>6706513</v>
+        <v>6706538</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882167</v>
+        <v>122882212</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626699</v>
+        <v>626670</v>
       </c>
       <c r="R21" t="n">
-        <v>6706548</v>
+        <v>6706513</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887301</v>
+        <v>122882189</v>
       </c>
       <c r="B22" t="n">
-        <v>95901</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,25 +2974,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
         <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706440</v>
+        <v>6706516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882270</v>
+        <v>122882318</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>95903</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626653</v>
+        <v>626645</v>
       </c>
       <c r="R23" t="n">
-        <v>6706538</v>
+        <v>6706570</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887165</v>
+        <v>122887268</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626634</v>
+        <v>626653</v>
       </c>
       <c r="R24" t="n">
-        <v>6706458</v>
+        <v>6706454</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882189</v>
+        <v>122882318</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,25 +2974,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626668</v>
+        <v>626645</v>
       </c>
       <c r="R22" t="n">
-        <v>6706516</v>
+        <v>6706570</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B23" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R23" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B22" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,25 +2974,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882189</v>
+        <v>122882318</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626668</v>
+        <v>626645</v>
       </c>
       <c r="R23" t="n">
-        <v>6706516</v>
+        <v>6706570</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122887317</v>
+        <v>122882167</v>
       </c>
       <c r="B14" t="n">
-        <v>57428</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,52 +2064,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626668</v>
+        <v>626699</v>
       </c>
       <c r="R14" t="n">
-        <v>6706440</v>
+        <v>6706548</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2141,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882235</v>
+        <v>122887244</v>
       </c>
       <c r="B15" t="n">
-        <v>74855</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626655</v>
+        <v>626638</v>
       </c>
       <c r="R15" t="n">
-        <v>6706513</v>
+        <v>6706452</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2253,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,7 +2276,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122887244</v>
+        <v>122882270</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2330,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626638</v>
+        <v>626653</v>
       </c>
       <c r="R16" t="n">
-        <v>6706452</v>
+        <v>6706538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2365,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887165</v>
+        <v>122887317</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>57428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,38 +2400,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626634</v>
+        <v>626668</v>
       </c>
       <c r="R17" t="n">
-        <v>6706458</v>
+        <v>6706440</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882167</v>
+        <v>122882189</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626699</v>
+        <v>626668</v>
       </c>
       <c r="R18" t="n">
-        <v>6706548</v>
+        <v>6706516</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2626,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122887301</v>
+        <v>122887268</v>
       </c>
       <c r="B19" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,25 +2638,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R19" t="n">
-        <v>6706440</v>
+        <v>6706454</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882270</v>
+        <v>122882318</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626653</v>
+        <v>626645</v>
       </c>
       <c r="R20" t="n">
-        <v>6706538</v>
+        <v>6706570</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882189</v>
+        <v>122887165</v>
       </c>
       <c r="B22" t="n">
         <v>98357</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626668</v>
+        <v>626634</v>
       </c>
       <c r="R22" t="n">
-        <v>6706516</v>
+        <v>6706458</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882318</v>
+        <v>122882235</v>
       </c>
       <c r="B23" t="n">
-        <v>95903</v>
+        <v>74855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626645</v>
+        <v>626655</v>
       </c>
       <c r="R23" t="n">
-        <v>6706570</v>
+        <v>6706513</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887268</v>
+        <v>122887301</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R24" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882318</v>
+        <v>122882212</v>
       </c>
       <c r="B20" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626645</v>
+        <v>626670</v>
       </c>
       <c r="R20" t="n">
-        <v>6706570</v>
+        <v>6706513</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882212</v>
+        <v>122882318</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,25 +2862,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626670</v>
+        <v>626645</v>
       </c>
       <c r="R21" t="n">
-        <v>6706513</v>
+        <v>6706570</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887165</v>
+        <v>122882235</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>74855</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,25 +2974,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626634</v>
+        <v>626655</v>
       </c>
       <c r="R22" t="n">
-        <v>6706458</v>
+        <v>6706513</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882235</v>
+        <v>122887165</v>
       </c>
       <c r="B23" t="n">
-        <v>74855</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626655</v>
+        <v>626634</v>
       </c>
       <c r="R23" t="n">
-        <v>6706513</v>
+        <v>6706458</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882167</v>
+        <v>122882318</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>95911</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626699</v>
+        <v>626645</v>
       </c>
       <c r="R14" t="n">
-        <v>6706548</v>
+        <v>6706570</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122887244</v>
+        <v>122882167</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626638</v>
+        <v>626699</v>
       </c>
       <c r="R15" t="n">
-        <v>6706452</v>
+        <v>6706548</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882270</v>
+        <v>122887301</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>95911</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R16" t="n">
-        <v>6706538</v>
+        <v>6706440</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887317</v>
+        <v>122882212</v>
       </c>
       <c r="B17" t="n">
-        <v>57428</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,52 +2400,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626668</v>
+        <v>626670</v>
       </c>
       <c r="R17" t="n">
-        <v>6706440</v>
+        <v>6706513</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882189</v>
+        <v>122887268</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R18" t="n">
-        <v>6706516</v>
+        <v>6706454</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122887268</v>
+        <v>122882235</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>74855</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,25 +2624,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626653</v>
+        <v>626655</v>
       </c>
       <c r="R19" t="n">
-        <v>6706454</v>
+        <v>6706513</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882212</v>
+        <v>122882270</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626670</v>
+        <v>626653</v>
       </c>
       <c r="R20" t="n">
-        <v>6706513</v>
+        <v>6706538</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2850,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B21" t="n">
-        <v>95903</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,25 +2848,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2890,10 +2876,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R21" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2962,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882235</v>
+        <v>122887317</v>
       </c>
       <c r="B22" t="n">
-        <v>74855</v>
+        <v>57428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,38 +2960,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626655</v>
+        <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706513</v>
+        <v>6706440</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,7 +3077,7 @@
         <v>122887165</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887301</v>
+        <v>122887244</v>
       </c>
       <c r="B24" t="n">
-        <v>95903</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626668</v>
+        <v>626638</v>
       </c>
       <c r="R24" t="n">
-        <v>6706440</v>
+        <v>6706452</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882318</v>
+        <v>122882167</v>
       </c>
       <c r="B14" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626645</v>
+        <v>626699</v>
       </c>
       <c r="R14" t="n">
-        <v>6706570</v>
+        <v>6706548</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882167</v>
+        <v>122882318</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626699</v>
+        <v>626645</v>
       </c>
       <c r="R15" t="n">
-        <v>6706548</v>
+        <v>6706570</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122887301</v>
+        <v>122882270</v>
       </c>
       <c r="B16" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R16" t="n">
-        <v>6706440</v>
+        <v>6706538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122882212</v>
+        <v>122887317</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,38 +2400,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626670</v>
+        <v>626668</v>
       </c>
       <c r="R17" t="n">
-        <v>6706513</v>
+        <v>6706440</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2514,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122887268</v>
+        <v>122887244</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2540,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626653</v>
+        <v>626638</v>
       </c>
       <c r="R18" t="n">
-        <v>6706454</v>
+        <v>6706452</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882235</v>
+        <v>122887165</v>
       </c>
       <c r="B19" t="n">
-        <v>74855</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,25 +2638,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626655</v>
+        <v>626634</v>
       </c>
       <c r="R19" t="n">
-        <v>6706513</v>
+        <v>6706458</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,7 +2738,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882270</v>
+        <v>122882212</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2764,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626653</v>
+        <v>626670</v>
       </c>
       <c r="R20" t="n">
-        <v>6706538</v>
+        <v>6706513</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2836,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882189</v>
+        <v>122882235</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>74855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,25 +2862,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2876,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626668</v>
+        <v>626655</v>
       </c>
       <c r="R21" t="n">
-        <v>6706516</v>
+        <v>6706513</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2948,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887317</v>
+        <v>122882189</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,42 +2974,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -3005,7 +3005,7 @@
         <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706440</v>
+        <v>6706516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,7 +3074,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887165</v>
+        <v>122887268</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626634</v>
+        <v>626653</v>
       </c>
       <c r="R23" t="n">
-        <v>6706458</v>
+        <v>6706454</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887244</v>
+        <v>122887301</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626638</v>
+        <v>626668</v>
       </c>
       <c r="R24" t="n">
-        <v>6706452</v>
+        <v>6706440</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887268</v>
+        <v>122887301</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R23" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887301</v>
+        <v>122887268</v>
       </c>
       <c r="B24" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R24" t="n">
-        <v>6706440</v>
+        <v>6706454</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2626,7 +2626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122887165</v>
+        <v>122882212</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626634</v>
+        <v>626670</v>
       </c>
       <c r="R19" t="n">
-        <v>6706458</v>
+        <v>6706513</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2738,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882212</v>
+        <v>122887165</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626670</v>
+        <v>626634</v>
       </c>
       <c r="R20" t="n">
-        <v>6706513</v>
+        <v>6706458</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887301</v>
+        <v>122887268</v>
       </c>
       <c r="B23" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R23" t="n">
-        <v>6706440</v>
+        <v>6706454</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887268</v>
+        <v>122887301</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R24" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882167</v>
+        <v>122882318</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626699</v>
+        <v>626645</v>
       </c>
       <c r="R14" t="n">
-        <v>6706548</v>
+        <v>6706570</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B15" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R15" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882270</v>
+        <v>122887268</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2319,7 +2319,7 @@
         <v>626653</v>
       </c>
       <c r="R16" t="n">
-        <v>6706538</v>
+        <v>6706454</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122887244</v>
+        <v>122882212</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626638</v>
+        <v>626670</v>
       </c>
       <c r="R18" t="n">
-        <v>6706452</v>
+        <v>6706513</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882212</v>
+        <v>122882167</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626670</v>
+        <v>626699</v>
       </c>
       <c r="R19" t="n">
-        <v>6706513</v>
+        <v>6706548</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122887165</v>
+        <v>122882270</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626634</v>
+        <v>626653</v>
       </c>
       <c r="R20" t="n">
-        <v>6706458</v>
+        <v>6706538</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882235</v>
+        <v>122887301</v>
       </c>
       <c r="B21" t="n">
-        <v>74855</v>
+        <v>95911</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,21 +2866,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626655</v>
+        <v>626668</v>
       </c>
       <c r="R21" t="n">
-        <v>6706513</v>
+        <v>6706440</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,7 +2962,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882189</v>
+        <v>122887165</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626668</v>
+        <v>626634</v>
       </c>
       <c r="R22" t="n">
-        <v>6706516</v>
+        <v>6706458</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,7 +3074,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887268</v>
+        <v>122887244</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626653</v>
+        <v>626638</v>
       </c>
       <c r="R23" t="n">
-        <v>6706454</v>
+        <v>6706452</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887301</v>
+        <v>122882235</v>
       </c>
       <c r="B24" t="n">
-        <v>95911</v>
+        <v>74855</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,21 +3202,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626668</v>
+        <v>626655</v>
       </c>
       <c r="R24" t="n">
-        <v>6706440</v>
+        <v>6706513</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B14" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R14" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882189</v>
+        <v>122882270</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R15" t="n">
-        <v>6706516</v>
+        <v>6706538</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122887268</v>
+        <v>122882212</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626653</v>
+        <v>626670</v>
       </c>
       <c r="R16" t="n">
-        <v>6706454</v>
+        <v>6706513</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887317</v>
+        <v>122887301</v>
       </c>
       <c r="B17" t="n">
-        <v>57428</v>
+        <v>95911</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,42 +2400,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102621</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -2477,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,7 +2500,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882212</v>
+        <v>122887244</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2554,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626670</v>
+        <v>626638</v>
       </c>
       <c r="R18" t="n">
-        <v>6706513</v>
+        <v>6706452</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2612,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882167</v>
+        <v>122887165</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2666,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626699</v>
+        <v>626634</v>
       </c>
       <c r="R19" t="n">
-        <v>6706548</v>
+        <v>6706458</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2724,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882270</v>
+        <v>122882167</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2778,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626653</v>
+        <v>626699</v>
       </c>
       <c r="R20" t="n">
-        <v>6706538</v>
+        <v>6706548</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2850,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122887301</v>
+        <v>122887317</v>
       </c>
       <c r="B21" t="n">
-        <v>95911</v>
+        <v>57428</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,28 +2848,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,7 +2962,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887165</v>
+        <v>122887268</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626634</v>
+        <v>626653</v>
       </c>
       <c r="R22" t="n">
-        <v>6706458</v>
+        <v>6706454</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887244</v>
+        <v>122882235</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>74855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626638</v>
+        <v>626655</v>
       </c>
       <c r="R23" t="n">
-        <v>6706452</v>
+        <v>6706513</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122882235</v>
+        <v>122882318</v>
       </c>
       <c r="B24" t="n">
-        <v>74855</v>
+        <v>95911</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,21 +3202,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626655</v>
+        <v>626645</v>
       </c>
       <c r="R24" t="n">
-        <v>6706513</v>
+        <v>6706570</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122887317</v>
+        <v>122887268</v>
       </c>
       <c r="B21" t="n">
-        <v>57428</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,52 +2848,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R21" t="n">
-        <v>6706440</v>
+        <v>6706454</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2925,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887268</v>
+        <v>122887317</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,38 +2960,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122882189</v>
+        <v>122887244</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626668</v>
+        <v>626638</v>
       </c>
       <c r="R14" t="n">
-        <v>6706516</v>
+        <v>6706452</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882270</v>
+        <v>122887268</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>626653</v>
       </c>
       <c r="R15" t="n">
-        <v>6706538</v>
+        <v>6706454</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882212</v>
+        <v>122882235</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>74858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626670</v>
+        <v>626655</v>
       </c>
       <c r="R16" t="n">
         <v>6706513</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887301</v>
+        <v>122882189</v>
       </c>
       <c r="B17" t="n">
-        <v>95911</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>626668</v>
       </c>
       <c r="R17" t="n">
-        <v>6706440</v>
+        <v>6706516</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122887244</v>
+        <v>122882212</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626638</v>
+        <v>626670</v>
       </c>
       <c r="R18" t="n">
-        <v>6706452</v>
+        <v>6706513</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122887165</v>
+        <v>122882167</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626634</v>
+        <v>626699</v>
       </c>
       <c r="R19" t="n">
-        <v>6706458</v>
+        <v>6706548</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882167</v>
+        <v>122887301</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>95914</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626699</v>
+        <v>626668</v>
       </c>
       <c r="R20" t="n">
-        <v>6706548</v>
+        <v>6706440</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122887268</v>
+        <v>122887317</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>57431</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,38 +2848,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R21" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2911,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2935,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122887317</v>
+        <v>122882318</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>95914</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,52 +2974,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626668</v>
+        <v>626645</v>
       </c>
       <c r="R22" t="n">
-        <v>6706440</v>
+        <v>6706570</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882235</v>
+        <v>122882270</v>
       </c>
       <c r="B23" t="n">
-        <v>74855</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626655</v>
+        <v>626653</v>
       </c>
       <c r="R23" t="n">
-        <v>6706513</v>
+        <v>6706538</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122882318</v>
+        <v>122887165</v>
       </c>
       <c r="B24" t="n">
-        <v>95911</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626645</v>
+        <v>626634</v>
       </c>
       <c r="R24" t="n">
-        <v>6706570</v>
+        <v>6706458</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122887244</v>
+        <v>122887301</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>95916</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626638</v>
+        <v>626668</v>
       </c>
       <c r="R14" t="n">
-        <v>6706452</v>
+        <v>6706440</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122887268</v>
+        <v>122882235</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>74858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626653</v>
+        <v>626655</v>
       </c>
       <c r="R15" t="n">
-        <v>6706454</v>
+        <v>6706513</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882235</v>
+        <v>122882189</v>
       </c>
       <c r="B16" t="n">
-        <v>74858</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626655</v>
+        <v>626668</v>
       </c>
       <c r="R16" t="n">
-        <v>6706513</v>
+        <v>6706516</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122882189</v>
+        <v>122887244</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626668</v>
+        <v>626638</v>
       </c>
       <c r="R17" t="n">
-        <v>6706516</v>
+        <v>6706452</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,7 +2503,7 @@
         <v>122882212</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>122882167</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122887301</v>
+        <v>122887268</v>
       </c>
       <c r="B20" t="n">
-        <v>95914</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R20" t="n">
-        <v>6706440</v>
+        <v>6706454</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122887317</v>
+        <v>122882270</v>
       </c>
       <c r="B21" t="n">
-        <v>57431</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,52 +2848,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626668</v>
+        <v>626653</v>
       </c>
       <c r="R21" t="n">
-        <v>6706440</v>
+        <v>6706538</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2925,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,7 +2951,7 @@
         <v>122882318</v>
       </c>
       <c r="B22" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3074,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882270</v>
+        <v>122887165</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626653</v>
+        <v>626634</v>
       </c>
       <c r="R23" t="n">
-        <v>6706538</v>
+        <v>6706458</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3149,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887165</v>
+        <v>122887317</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>57431</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,38 +3184,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626634</v>
+        <v>626668</v>
       </c>
       <c r="R24" t="n">
-        <v>6706458</v>
+        <v>6706440</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882235</v>
+        <v>122882189</v>
       </c>
       <c r="B15" t="n">
-        <v>74858</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626655</v>
+        <v>626668</v>
       </c>
       <c r="R15" t="n">
-        <v>6706513</v>
+        <v>6706516</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882189</v>
+        <v>122882235</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>74858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626668</v>
+        <v>626655</v>
       </c>
       <c r="R16" t="n">
-        <v>6706516</v>
+        <v>6706513</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122887301</v>
+        <v>122882235</v>
       </c>
       <c r="B14" t="n">
-        <v>95916</v>
+        <v>74858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626668</v>
+        <v>626655</v>
       </c>
       <c r="R14" t="n">
-        <v>6706440</v>
+        <v>6706513</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882189</v>
+        <v>122882167</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626668</v>
+        <v>626699</v>
       </c>
       <c r="R15" t="n">
-        <v>6706516</v>
+        <v>6706548</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122882235</v>
+        <v>122887244</v>
       </c>
       <c r="B16" t="n">
-        <v>74858</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626655</v>
+        <v>626638</v>
       </c>
       <c r="R16" t="n">
-        <v>6706513</v>
+        <v>6706452</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122887244</v>
+        <v>122882270</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626638</v>
+        <v>626653</v>
       </c>
       <c r="R17" t="n">
-        <v>6706452</v>
+        <v>6706538</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882212</v>
+        <v>122887268</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626670</v>
+        <v>626653</v>
       </c>
       <c r="R18" t="n">
-        <v>6706513</v>
+        <v>6706454</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882167</v>
+        <v>122887301</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,25 +2624,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626699</v>
+        <v>626668</v>
       </c>
       <c r="R19" t="n">
-        <v>6706548</v>
+        <v>6706440</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122887268</v>
+        <v>122887317</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,38 +2736,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626653</v>
+        <v>626668</v>
       </c>
       <c r="R20" t="n">
-        <v>6706454</v>
+        <v>6706440</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122882270</v>
+        <v>122887165</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626653</v>
+        <v>626634</v>
       </c>
       <c r="R21" t="n">
-        <v>6706538</v>
+        <v>6706458</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2911,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2935,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882318</v>
+        <v>122882189</v>
       </c>
       <c r="B22" t="n">
-        <v>95916</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,25 +2974,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626645</v>
+        <v>626668</v>
       </c>
       <c r="R22" t="n">
-        <v>6706570</v>
+        <v>6706516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3060,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122887165</v>
+        <v>122882318</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,25 +3086,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626634</v>
+        <v>626645</v>
       </c>
       <c r="R23" t="n">
-        <v>6706458</v>
+        <v>6706570</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3135,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122887317</v>
+        <v>122882212</v>
       </c>
       <c r="B24" t="n">
-        <v>57431</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,52 +3198,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626668</v>
+        <v>626670</v>
       </c>
       <c r="R24" t="n">
-        <v>6706440</v>
+        <v>6706513</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3296,6 +3296,2467 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126315241</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626668</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6706493</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126315591</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626698</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6706559</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126315510</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626686</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6706541</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126315537</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626701</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6706540</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126315121</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626638</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6706471</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126315306</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>626676</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6706514</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126314884</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626656</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6706401</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126315219</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626658</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6706489</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126314915</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95794</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>210</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>626627</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6706427</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126315578</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>626709</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6706556</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126314937</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>626627</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6706427</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126315147</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626647</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6706468</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126315762</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>626660</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6706617</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126315157</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626656</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6706484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126315454</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626680</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6706534</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126315192</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>626673</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6706475</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126315175</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>53</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626656</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6706484</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126315134</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626645</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6706475</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126315080</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626638</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6706438</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126314970</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>53</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626619</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6706438</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126315255</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626673</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6706493</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126315465</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626682</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6706538</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126315482</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91252</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626682</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6706535</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3298,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126315241</v>
+        <v>126315591</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626668</v>
+        <v>626698</v>
       </c>
       <c r="R25" t="n">
-        <v>6706493</v>
+        <v>6706559</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,10 +3405,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126315591</v>
+        <v>126315241</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626698</v>
+        <v>626668</v>
       </c>
       <c r="R26" t="n">
-        <v>6706559</v>
+        <v>6706493</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,10 +3512,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315510</v>
+        <v>126315121</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626686</v>
+        <v>626638</v>
       </c>
       <c r="R27" t="n">
-        <v>6706541</v>
+        <v>6706471</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,32 +3619,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315537</v>
+        <v>126315510</v>
       </c>
       <c r="B28" t="n">
-        <v>96598</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626701</v>
+        <v>626686</v>
       </c>
       <c r="R28" t="n">
-        <v>6706540</v>
+        <v>6706541</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315121</v>
+        <v>126315537</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626638</v>
+        <v>626701</v>
       </c>
       <c r="R29" t="n">
-        <v>6706471</v>
+        <v>6706540</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,7 +3836,7 @@
         <v>126315306</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126314884</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126315219</v>
+        <v>126314915</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>95798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626658</v>
+        <v>626627</v>
       </c>
       <c r="R32" t="n">
-        <v>6706489</v>
+        <v>6706427</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,32 +4154,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126314915</v>
+        <v>126315219</v>
       </c>
       <c r="B33" t="n">
-        <v>95794</v>
+        <v>98349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626627</v>
+        <v>626658</v>
       </c>
       <c r="R33" t="n">
-        <v>6706427</v>
+        <v>6706489</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,7 +4264,7 @@
         <v>126315578</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126314937</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126315147</v>
+        <v>126315762</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626647</v>
+        <v>626660</v>
       </c>
       <c r="R36" t="n">
-        <v>6706468</v>
+        <v>6706617</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4582,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126315762</v>
+        <v>126315147</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626660</v>
+        <v>626647</v>
       </c>
       <c r="R37" t="n">
-        <v>6706617</v>
+        <v>6706468</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126315157</v>
+        <v>126315454</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626656</v>
+        <v>626680</v>
       </c>
       <c r="R38" t="n">
-        <v>6706484</v>
+        <v>6706534</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126315454</v>
+        <v>126315157</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626680</v>
+        <v>626656</v>
       </c>
       <c r="R39" t="n">
-        <v>6706534</v>
+        <v>6706484</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4906,7 +4906,7 @@
         <v>126315192</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>126315175</v>
       </c>
       <c r="B41" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126315134</v>
+        <v>126315080</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626645</v>
+        <v>626638</v>
       </c>
       <c r="R42" t="n">
-        <v>6706475</v>
+        <v>6706438</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5224,10 +5224,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126315080</v>
+        <v>126315134</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626638</v>
+        <v>626645</v>
       </c>
       <c r="R43" t="n">
-        <v>6706438</v>
+        <v>6706475</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126314970</v>
+        <v>126315255</v>
       </c>
       <c r="B44" t="n">
-        <v>96598</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626619</v>
+        <v>626673</v>
       </c>
       <c r="R44" t="n">
-        <v>6706438</v>
+        <v>6706493</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5438,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126315255</v>
+        <v>126314970</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626673</v>
+        <v>626619</v>
       </c>
       <c r="R45" t="n">
-        <v>6706493</v>
+        <v>6706438</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,32 +5545,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126315465</v>
+        <v>126315482</v>
       </c>
       <c r="B46" t="n">
-        <v>98345</v>
+        <v>91256</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5583,7 +5583,7 @@
         <v>626682</v>
       </c>
       <c r="R46" t="n">
-        <v>6706538</v>
+        <v>6706535</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5652,32 +5652,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126315482</v>
+        <v>126315465</v>
       </c>
       <c r="B47" t="n">
-        <v>91252</v>
+        <v>98349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
         <v>626682</v>
       </c>
       <c r="R47" t="n">
-        <v>6706535</v>
+        <v>6706538</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3301,7 +3301,7 @@
         <v>126315591</v>
       </c>
       <c r="B25" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>126315241</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315121</v>
+        <v>126315537</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>96605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626638</v>
+        <v>626701</v>
       </c>
       <c r="R27" t="n">
-        <v>6706471</v>
+        <v>6706540</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315510</v>
+        <v>126315121</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626686</v>
+        <v>626638</v>
       </c>
       <c r="R28" t="n">
-        <v>6706541</v>
+        <v>6706471</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315537</v>
+        <v>126315510</v>
       </c>
       <c r="B29" t="n">
-        <v>96602</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626701</v>
+        <v>626686</v>
       </c>
       <c r="R29" t="n">
-        <v>6706540</v>
+        <v>6706541</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3836,7 +3836,7 @@
         <v>126315306</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126314884</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>126314915</v>
       </c>
       <c r="B32" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>126315219</v>
       </c>
       <c r="B33" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>126315578</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126314937</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>126315762</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>126315147</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>126315454</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>126315157</v>
       </c>
       <c r="B39" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>126315192</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>126315175</v>
       </c>
       <c r="B41" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>126315080</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>126315134</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126315255</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>126314970</v>
       </c>
       <c r="B45" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126315465</v>
       </c>
       <c r="B47" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315537</v>
+        <v>126315121</v>
       </c>
       <c r="B27" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626701</v>
+        <v>626638</v>
       </c>
       <c r="R27" t="n">
-        <v>6706540</v>
+        <v>6706471</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315121</v>
+        <v>126315510</v>
       </c>
       <c r="B28" t="n">
         <v>98352</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626638</v>
+        <v>626686</v>
       </c>
       <c r="R28" t="n">
-        <v>6706471</v>
+        <v>6706541</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315510</v>
+        <v>126315537</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626686</v>
+        <v>626701</v>
       </c>
       <c r="R29" t="n">
-        <v>6706541</v>
+        <v>6706540</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -5331,32 +5331,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126315255</v>
+        <v>126314970</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626673</v>
+        <v>626619</v>
       </c>
       <c r="R44" t="n">
-        <v>6706493</v>
+        <v>6706438</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5438,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126314970</v>
+        <v>126315255</v>
       </c>
       <c r="B45" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626619</v>
+        <v>626673</v>
       </c>
       <c r="R45" t="n">
-        <v>6706438</v>
+        <v>6706493</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315121</v>
+        <v>126315537</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626638</v>
+        <v>626701</v>
       </c>
       <c r="R27" t="n">
-        <v>6706471</v>
+        <v>6706540</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315537</v>
+        <v>126315121</v>
       </c>
       <c r="B29" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626701</v>
+        <v>626638</v>
       </c>
       <c r="R29" t="n">
-        <v>6706540</v>
+        <v>6706471</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126314970</v>
+        <v>126315255</v>
       </c>
       <c r="B44" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626619</v>
+        <v>626673</v>
       </c>
       <c r="R44" t="n">
-        <v>6706438</v>
+        <v>6706493</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5438,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126315255</v>
+        <v>126314970</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626673</v>
+        <v>626619</v>
       </c>
       <c r="R45" t="n">
-        <v>6706493</v>
+        <v>6706438</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -4047,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126314915</v>
+        <v>126315219</v>
       </c>
       <c r="B32" t="n">
-        <v>95801</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626627</v>
+        <v>626658</v>
       </c>
       <c r="R32" t="n">
-        <v>6706427</v>
+        <v>6706489</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,32 +4154,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126315219</v>
+        <v>126314915</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>95801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626658</v>
+        <v>626627</v>
       </c>
       <c r="R33" t="n">
-        <v>6706489</v>
+        <v>6706427</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3301,7 +3301,7 @@
         <v>126315591</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>126315241</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315537</v>
+        <v>126315510</v>
       </c>
       <c r="B27" t="n">
-        <v>96605</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626701</v>
+        <v>626686</v>
       </c>
       <c r="R27" t="n">
-        <v>6706540</v>
+        <v>6706541</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315510</v>
+        <v>126315121</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626686</v>
+        <v>626638</v>
       </c>
       <c r="R28" t="n">
-        <v>6706541</v>
+        <v>6706471</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315121</v>
+        <v>126315537</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>96614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626638</v>
+        <v>626701</v>
       </c>
       <c r="R29" t="n">
-        <v>6706471</v>
+        <v>6706540</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,7 +3836,7 @@
         <v>126315306</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126314884</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126315219</v>
+        <v>126314915</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>95810</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626658</v>
+        <v>626627</v>
       </c>
       <c r="R32" t="n">
-        <v>6706489</v>
+        <v>6706427</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,32 +4154,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126314915</v>
+        <v>126315219</v>
       </c>
       <c r="B33" t="n">
-        <v>95801</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626627</v>
+        <v>626658</v>
       </c>
       <c r="R33" t="n">
-        <v>6706427</v>
+        <v>6706489</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,7 +4264,7 @@
         <v>126315578</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126314937</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>126315762</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>126315147</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126315454</v>
+        <v>126315157</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626680</v>
+        <v>626656</v>
       </c>
       <c r="R38" t="n">
-        <v>6706534</v>
+        <v>6706484</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126315157</v>
+        <v>126315454</v>
       </c>
       <c r="B39" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626656</v>
+        <v>626680</v>
       </c>
       <c r="R39" t="n">
-        <v>6706484</v>
+        <v>6706534</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4906,7 +4906,7 @@
         <v>126315192</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,32 +5010,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126315175</v>
+        <v>126315080</v>
       </c>
       <c r="B41" t="n">
-        <v>96605</v>
+        <v>98361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626656</v>
+        <v>626638</v>
       </c>
       <c r="R41" t="n">
-        <v>6706484</v>
+        <v>6706438</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5117,10 +5117,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126315080</v>
+        <v>126315134</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626638</v>
+        <v>626645</v>
       </c>
       <c r="R42" t="n">
-        <v>6706438</v>
+        <v>6706475</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5224,32 +5224,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126315134</v>
+        <v>126315175</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>96614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626645</v>
+        <v>626656</v>
       </c>
       <c r="R43" t="n">
-        <v>6706475</v>
+        <v>6706484</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5334,7 +5334,7 @@
         <v>126315255</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>126314970</v>
       </c>
       <c r="B45" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>126315482</v>
       </c>
       <c r="B46" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126315465</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3512,7 +3512,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315510</v>
+        <v>126315121</v>
       </c>
       <c r="B27" t="n">
         <v>98361</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626686</v>
+        <v>626638</v>
       </c>
       <c r="R27" t="n">
-        <v>6706541</v>
+        <v>6706471</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315121</v>
+        <v>126315510</v>
       </c>
       <c r="B28" t="n">
         <v>98361</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626638</v>
+        <v>626686</v>
       </c>
       <c r="R28" t="n">
-        <v>6706471</v>
+        <v>6706541</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4047,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126314915</v>
+        <v>126315219</v>
       </c>
       <c r="B32" t="n">
-        <v>95810</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626627</v>
+        <v>626658</v>
       </c>
       <c r="R32" t="n">
-        <v>6706427</v>
+        <v>6706489</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,32 +4154,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126315219</v>
+        <v>126314915</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>95810</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626658</v>
+        <v>626627</v>
       </c>
       <c r="R33" t="n">
-        <v>6706489</v>
+        <v>6706427</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4689,7 +4689,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126315157</v>
+        <v>126315454</v>
       </c>
       <c r="B38" t="n">
         <v>98361</v>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626656</v>
+        <v>626680</v>
       </c>
       <c r="R38" t="n">
-        <v>6706484</v>
+        <v>6706534</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,7 +4796,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126315454</v>
+        <v>126315157</v>
       </c>
       <c r="B39" t="n">
         <v>98361</v>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626680</v>
+        <v>626656</v>
       </c>
       <c r="R39" t="n">
-        <v>6706534</v>
+        <v>6706484</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5010,32 +5010,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126315080</v>
+        <v>126315175</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626638</v>
+        <v>626656</v>
       </c>
       <c r="R41" t="n">
-        <v>6706438</v>
+        <v>6706484</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126315134</v>
+        <v>126315080</v>
       </c>
       <c r="B42" t="n">
         <v>98361</v>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626645</v>
+        <v>626638</v>
       </c>
       <c r="R42" t="n">
-        <v>6706475</v>
+        <v>6706438</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5224,32 +5224,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126315175</v>
+        <v>126315134</v>
       </c>
       <c r="B43" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626656</v>
+        <v>626645</v>
       </c>
       <c r="R43" t="n">
-        <v>6706484</v>
+        <v>6706475</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126315255</v>
+        <v>126314970</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626673</v>
+        <v>626619</v>
       </c>
       <c r="R44" t="n">
-        <v>6706493</v>
+        <v>6706438</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5438,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126314970</v>
+        <v>126315255</v>
       </c>
       <c r="B45" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626619</v>
+        <v>626673</v>
       </c>
       <c r="R45" t="n">
-        <v>6706438</v>
+        <v>6706493</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,32 +5545,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126315482</v>
+        <v>126315465</v>
       </c>
       <c r="B46" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5583,7 +5583,7 @@
         <v>626682</v>
       </c>
       <c r="R46" t="n">
-        <v>6706535</v>
+        <v>6706538</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5652,32 +5652,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126315465</v>
+        <v>126315482</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
         <v>626682</v>
       </c>
       <c r="R47" t="n">
-        <v>6706538</v>
+        <v>6706535</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315121</v>
+        <v>126315537</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626638</v>
+        <v>626701</v>
       </c>
       <c r="R27" t="n">
-        <v>6706471</v>
+        <v>6706540</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315510</v>
+        <v>126315121</v>
       </c>
       <c r="B28" t="n">
         <v>98361</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626686</v>
+        <v>626638</v>
       </c>
       <c r="R28" t="n">
-        <v>6706541</v>
+        <v>6706471</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315537</v>
+        <v>126315510</v>
       </c>
       <c r="B29" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626701</v>
+        <v>626686</v>
       </c>
       <c r="R29" t="n">
-        <v>6706540</v>
+        <v>6706541</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 55561-2024 artfynd.xlsx
+++ b/artfynd/A 55561-2024 artfynd.xlsx
@@ -3512,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126315537</v>
+        <v>126315121</v>
       </c>
       <c r="B27" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626701</v>
+        <v>626638</v>
       </c>
       <c r="R27" t="n">
-        <v>6706540</v>
+        <v>6706471</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126315121</v>
+        <v>126315510</v>
       </c>
       <c r="B28" t="n">
         <v>98361</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626638</v>
+        <v>626686</v>
       </c>
       <c r="R28" t="n">
-        <v>6706471</v>
+        <v>6706541</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126315510</v>
+        <v>126315537</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626686</v>
+        <v>626701</v>
       </c>
       <c r="R29" t="n">
-        <v>6706541</v>
+        <v>6706540</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
